--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2240,60 @@
       <c r="E39" s="20" t="inlineStr">
         <is>
           <t>신규 강사 등록 시 국적·연락처를 함께 채워 두면 이후 문의가 확 줄어듭니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>🗂️</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요). → 명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요. → 적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요. → 강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요. → 급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>학부모 월간 성적표 (오각형) 발송</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요. → 학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요. → 오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요. → 주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F408"/>
+  <dimension ref="A1:F436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6795,11 +6849,334 @@
       <c r="E408" s="33" t="n"/>
       <c r="F408" s="33" t="n"/>
     </row>
+    <row r="410" ht="26" customHeight="1">
+      <c r="A410" s="21" t="inlineStr">
+        <is>
+          <t>37  🗂️ 강사 통합 관리 개편 (명부 필터 · 그룹 · 상세 탭)  —  찾기 쉬운 명부 · 한눈에 보는 상세</t>
+        </is>
+      </c>
+      <c r="B410" s="22" t="n"/>
+      <c r="C410" s="22" t="n"/>
+      <c r="D410" s="22" t="n"/>
+      <c r="E410" s="22" t="n"/>
+      <c r="F410" s="22" t="n"/>
+    </row>
+    <row r="411" ht="42" customHeight="1">
+      <c r="A411" s="23" t="inlineStr">
+        <is>
+          <t>📖 강사 관리 화면이 찾기 쉽고 보기 편하게 정리됐어요. 흩어져 있던 메뉴를 네 묶음으로 그룹지어 사이드바에 담았고, 강사 명부 위에는 구분·상태·그룹 드롭다운 필터와 적용된 필터 칩이 생겼어요. 강사를 누르면 프로필·급여·평가 탭으로 나뉜 상세 화면이 열리고, 매니저 배지와 재직 상태(재직·휴직·퇴사) 가 한눈에 표시돼요.</t>
+        </is>
+      </c>
+      <c r="B411" s="24" t="n"/>
+      <c r="C411" s="24" t="n"/>
+      <c r="D411" s="24" t="n"/>
+      <c r="E411" s="24" t="n"/>
+      <c r="F411" s="24" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B412" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="30" customHeight="1">
+      <c r="A413" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B413" s="28" t="inlineStr">
+        <is>
+          <t>관리자 메뉴 강사 통합을 열어요(메뉴가 네 묶음으로 정리돼 있어요).</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="30" customHeight="1">
+      <c r="A414" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B414" s="28" t="inlineStr">
+        <is>
+          <t>명부 위 상태·그룹 드롭다운으로 원하는 강사만 걸러요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="30" customHeight="1">
+      <c r="A415" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B415" s="28" t="inlineStr">
+        <is>
+          <t>적용된 필터는 칩으로 표시되고, 칩을 지우면 해제돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="30" customHeight="1">
+      <c r="A416" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B416" s="28" t="inlineStr">
+        <is>
+          <t>강사를 누르면 프로필 / 급여 / 평가 탭 상세가 열려요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="30" customHeight="1">
+      <c r="A417" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B417" s="28" t="inlineStr">
+        <is>
+          <t>급여·평가 탭의 요약 숫자는 열 때 필요한 만큼만 불러옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="24" customHeight="1">
+      <c r="A418" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B418" s="30" t="inlineStr">
+        <is>
+          <t>매니저는 배지로 구분되고, 재직 상태가 재직·휴직·퇴사 3가지로 표시돼요.</t>
+        </is>
+      </c>
+      <c r="C418" s="31" t="n"/>
+      <c r="D418" s="31" t="n"/>
+      <c r="E418" s="31" t="n"/>
+      <c r="F418" s="31" t="n"/>
+    </row>
+    <row r="419" ht="24" customHeight="1">
+      <c r="A419" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B419" s="30" t="inlineStr">
+        <is>
+          <t>이름이 비어도 아이디로 대체 표기돼 빈칸이 없어요.</t>
+        </is>
+      </c>
+      <c r="C419" s="31" t="n"/>
+      <c r="D419" s="31" t="n"/>
+      <c r="E419" s="31" t="n"/>
+      <c r="F419" s="31" t="n"/>
+    </row>
+    <row r="420" ht="24" customHeight="1">
+      <c r="A420" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B420" s="30" t="inlineStr">
+        <is>
+          <t>상세 탭은 기존 API를 재사용해 빠르게 뜨고, 화면은 한/영 병기예요.</t>
+        </is>
+      </c>
+      <c r="C420" s="31" t="n"/>
+      <c r="D420" s="31" t="n"/>
+      <c r="E420" s="31" t="n"/>
+      <c r="F420" s="31" t="n"/>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B421" s="30" t="inlineStr">
+        <is>
+          <t>중복이던 급여 입구를 정리하고 버그 접수는 별도 시스템으로 옮겼어요.</t>
+        </is>
+      </c>
+      <c r="C421" s="31" t="n"/>
+      <c r="D421" s="31" t="n"/>
+      <c r="E421" s="31" t="n"/>
+      <c r="F421" s="31" t="n"/>
+    </row>
+    <row r="422" ht="26" customHeight="1">
+      <c r="A422" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 필터·상세 정리 작업이에요. 강사 등록·수정·삭제 기능 자체는 그대로예요.</t>
+        </is>
+      </c>
+      <c r="B422" s="35" t="n"/>
+      <c r="C422" s="35" t="n"/>
+      <c r="D422" s="35" t="n"/>
+      <c r="E422" s="35" t="n"/>
+      <c r="F422" s="35" t="n"/>
+    </row>
+    <row r="423" ht="30" customHeight="1">
+      <c r="A423" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 강사가 많을수록 상태·그룹 필터가 큰 힘을 발휘해요. 자주 보는 조건은 필터를 걸어 두고 쓰세요.</t>
+        </is>
+      </c>
+      <c r="B423" s="33" t="n"/>
+      <c r="C423" s="33" t="n"/>
+      <c r="D423" s="33" t="n"/>
+      <c r="E423" s="33" t="n"/>
+      <c r="F423" s="33" t="n"/>
+    </row>
+    <row r="425" ht="26" customHeight="1">
+      <c r="A425" s="21" t="inlineStr">
+        <is>
+          <t>38  🌟 학부모 월간 성적표 (오각형) 발송  —  5축 그래프 성적표를 미리보고 링크로</t>
+        </is>
+      </c>
+      <c r="B425" s="22" t="n"/>
+      <c r="C425" s="22" t="n"/>
+      <c r="D425" s="22" t="n"/>
+      <c r="E425" s="22" t="n"/>
+      <c r="F425" s="22" t="n"/>
+    </row>
+    <row r="426" ht="42" customHeight="1">
+      <c r="A426" s="23" t="inlineStr">
+        <is>
+          <t>📖 학부모에게 보내는 월간 성적표가 오각형 5축 그래프로 새로워졌어요. 발음·유창성 / 어휘 / 문장 구성력 / 수업 태도 / 참여도 를 한눈에 보여 주고, 출결·판단력·담임의 한마디가 함께 담깁니다. 관리자·교사는 학생 ID와 월을 넣어 미리보기한 뒤 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+      <c r="B426" s="24" t="n"/>
+      <c r="C426" s="24" t="n"/>
+      <c r="D426" s="24" t="n"/>
+      <c r="E426" s="24" t="n"/>
+      <c r="F426" s="24" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="25" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B427" s="26" t="inlineStr">
+        <is>
+          <t>할 일</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="30" customHeight="1">
+      <c r="A428" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B428" s="28" t="inlineStr">
+        <is>
+          <t>월간 리포트 화면을 열어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>학생 ID와 월을 넣고 레포트 보기를 눌러 미리봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>오각형과 담임의 한마디를 확인하고, 필요하면 평가를 보완해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="30" customHeight="1">
+      <c r="A431" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B431" s="28" t="inlineStr">
+        <is>
+          <t>주소에 ?uid=학생ID&amp;period=YYYY-MM 를 붙여 카카오톡 링크로 보냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B432" s="30" t="inlineStr">
+        <is>
+          <t>실제 기록이 있는 축만 채워져 신뢰할 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C432" s="31" t="n"/>
+      <c r="D432" s="31" t="n"/>
+      <c r="E432" s="31" t="n"/>
+      <c r="F432" s="31" t="n"/>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>2개월 주기로 정리해 학부모 피로 없이 변화를 전달해요.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B434" s="30" t="inlineStr">
+        <is>
+          <t>인쇄/PDF 버튼으로 상담용 종이 성적표도 즉시 만들 수 있어요.</t>
+        </is>
+      </c>
+      <c r="C434" s="31" t="n"/>
+      <c r="D434" s="31" t="n"/>
+      <c r="E434" s="31" t="n"/>
+      <c r="F434" s="31" t="n"/>
+    </row>
+    <row r="435" ht="26" customHeight="1">
+      <c r="A435" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ 알아두기 · 성적표 열람은 승인 게이트를 거쳐요. 관리자는 로그인 세션으로, 학부모는 발급된 링크(토큰)로만 열립니다.</t>
+        </is>
+      </c>
+      <c r="B435" s="35" t="n"/>
+      <c r="C435" s="35" t="n"/>
+      <c r="D435" s="35" t="n"/>
+      <c r="E435" s="35" t="n"/>
+      <c r="F435" s="35" t="n"/>
+    </row>
+    <row r="436" ht="30" customHeight="1">
+      <c r="A436" s="32" t="inlineStr">
+        <is>
+          <t>💡 꿀팁 · 상담 예약과 함께 성적표 링크를 미리 보내면 상담이 훨씬 매끄러워요.</t>
+        </is>
+      </c>
+      <c r="B436" s="33" t="n"/>
+      <c r="C436" s="33" t="n"/>
+      <c r="D436" s="33" t="n"/>
+      <c r="E436" s="33" t="n"/>
+      <c r="F436" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="372">
+  <mergeCells count="398">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A394:F394"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B238:F238"/>
@@ -6814,15 +7191,19 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B418:F418"/>
     <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="A267:F267"/>
+    <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="B293:F293"/>
     <mergeCell ref="A135:F135"/>
@@ -6830,6 +7211,7 @@
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B317:F317"/>
     <mergeCell ref="B388:F388"/>
@@ -6919,6 +7301,7 @@
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B412:F412"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="A311:F311"/>
@@ -6955,12 +7338,15 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
     <mergeCell ref="B364:F364"/>
+    <mergeCell ref="B413:F413"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="B222:F222"/>
+    <mergeCell ref="B415:F415"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
@@ -6970,6 +7356,7 @@
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A426:F426"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B248:F248"/>
@@ -6988,8 +7375,10 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="A408:F408"/>
     <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A423:F423"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B365:F365"/>
     <mergeCell ref="B292:F292"/>
@@ -6997,18 +7386,22 @@
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B294:F294"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A436:F436"/>
     <mergeCell ref="A357:F357"/>
     <mergeCell ref="A258:F258"/>
     <mergeCell ref="A329:F329"/>
     <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B434:F434"/>
     <mergeCell ref="A358:F358"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B313:F313"/>
@@ -7016,12 +7409,14 @@
     <mergeCell ref="B378:F378"/>
     <mergeCell ref="B305:F305"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A422:F422"/>
     <mergeCell ref="A360:F360"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="A149:F149"/>
     <mergeCell ref="A385:F385"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A411:F411"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
@@ -7108,6 +7503,7 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="A278:F278"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B162:F162"/>
@@ -7116,10 +7512,12 @@
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="B216:F216"/>
+    <mergeCell ref="B414:F414"/>
     <mergeCell ref="A398:F398"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="B280:F280"/>
     <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B416:F416"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B295:F295"/>
     <mergeCell ref="B282:F282"/>
@@ -7155,13 +7553,17 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B417:F417"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B367:F367"/>
+    <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="B354:F354"/>
     <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B285:F285"/>
     <mergeCell ref="B64:F64"/>

--- a/cloudflare-deploy/public/library/admin/admin-kr.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-kr.xlsx
@@ -1111,6 +1111,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1241</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="3162300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1261</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="4552950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1288</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="2181225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1327</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="3829050"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1351</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="1200150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1413,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2797,6 +2947,213 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>10-1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>대리점 로그인 · 메뉴 열기</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>• 대리점 아이디로 mangoi.ai/admin/login 에 로그인하면 대리점 화면이 열립니다.
+• ④ 왼쪽 메뉴 정산통계관리 › 🤖 AI 컨텐츠 결제. 이 메뉴는 대리점 계정에만 보입니다(본사·지사 계정에는 없습니다).
+• 본사는 정산·매출 › 🏢 AI 사용료(A.i 학습 사용료 관리)에서 학원별 인원·예상 청구액을 보고, 예외 단가를 정하고, 자동 청구 켜기/끄기를 합니다. 결제 버튼은 거기에 없습니다.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>학생 명단 불러오기</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>• 위의 결제 마감(이번 달 말일 · D-남은 날)을 확인합니다. 결제하는 것은 다음 달 이용분입니다.
+• 숫자 칸: A.i 이용 신청(결제 대상) · 아직 신청 안 함 · 화상영어(포함) — 화상영어 학생은 수업료에 A.i 가 포함돼 여기서 결제하지 않습니다.
+• ⑤ 우리 학원 학생 불러와서 고르기는 명단만 불러옵니다. 이때는 아무것도 결제되지 않습니다.
+• 본사가 자동 청구를 아직 켜지 않았으면 «본사가 아직 A.i 컨텐츠 결제를 열지 않았습니다(테스트 기간)» 만 보입니다 — 고장이 아닙니다.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>다음 달에 쓸 학생 고르기</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>• ⑥ 결제 대상에 체크된 학생만 결제됩니다. 그만둔 학생은 체크를 풀면 결제 전에 빠집니다.
+• 이름·아이디로 찾을 수 있고, 보이는 학생 모두 빼기 / 모두 선택으로 한 번에 바꿉니다(몇 명이 바뀌는지 먼저 묻습니다).
+• 체크를 바꿀 때마다 금액은 서버가 다시 계산합니다.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>아직 신청 안 한 학생 · 화상영어 학생</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>• ⑦ 아직 신청 안 한 학생 중 다음 달에 쓸 학생을 체크하면 결제 대상에 들어갑니다.
+• 📹 화상영어 수업 학생은 접혀 있습니다. A.i 가 수업료에 포함돼 고르지 않습니다 — 판정이 틀린 학생만 체크합니다.
+• 학원이 직접 바꾼 학생에는 «✔ 학원 확인» 표시가 붙고, 그 뒤로는 자동 분류가 바꾸지 않습니다.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>금액 확인 · 카드 결제</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>• ⑧ 합계 인원·금액을 확인하고 ⑨ OOO원 결제하기 → 확인창 → 토스 카드 결제창에서 결제합니다.
+• 1명 단가(한 달): 20명 이하 7,500원 · 21~50명 6,500원 · 51~70명 5,500원 · 71명 이상 4,500원. 최소 청구는 없습니다(2026-10-26부터).
+• 인원이 늘어도 총액은 줄지 않게 계산됩니다(예: 21~23명은 150,000원). 금액은 결제하는 순간 서버가 다시 계산합니다 — 화면 숫자는 표시용입니다. 본사가 «예외 단가»를 정한 학원은 그 단가 × 인원입니다.
+• 시연 계정(testagency)은 결제창이 열리지 않습니다(예시 데이터).</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>AI 컨텐츠 결제 (대리점)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>결제 확인 · 추가 결제</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>• ⑩ 지난 결제에 ✅ 가 있으면 결제 완료입니다. 결제가 끝나면 «결제가 완료됐습니다» 가 뜨고 낸 학생은 위에 고정됩니다.
+• 같은 달에 학생을 더 넣으면 아래에서 체크하고 추가 결제 — 늘어난 학생 몫만 냅니다.
+• 이미 결제한 학생은 화면에서 빼거나 바꿀 수 없습니다. 환불은 본사가 처리합니다.
+• 아직 안 낸 지난 달이 있으면 맨 위에 «⚠️ 아직 결제하지 않은 달이 있습니다» 버튼이 나옵니다.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>화면그림!10-6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2808,7 +3165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1209"/>
+  <dimension ref="A1:A1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3084,6 +3441,48 @@
       <c r="A1209" s="3" t="inlineStr">
         <is>
           <t>9-2  매일보고</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="3" t="inlineStr">
+        <is>
+          <t>10-1  대리점 로그인 · 메뉴 열기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="3" t="inlineStr">
+        <is>
+          <t>10-2  학생 명단 불러오기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="3" t="inlineStr">
+        <is>
+          <t>10-3  다음 달에 쓸 학생 고르기</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="3" t="inlineStr">
+        <is>
+          <t>10-4  아직 신청 안 한 학생 · 화상영어 학생</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="3" t="inlineStr">
+        <is>
+          <t>10-5  금액 확인 · 카드 결제</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="3" t="inlineStr">
+        <is>
+          <t>10-6  결제 확인 · 추가 결제</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3214,6 +3613,42 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>대리점이 «AI 컨텐츠 결제» 메뉴가 없대요</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>대리점 아이디로 로그인했는지 확인하세요. 그 메뉴는 대리점 계정에만 보입니다(지사·본사 계정에는 없음).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>대리점 화면에 «본사가 아직 A.i 컨텐츠 결제를 열지 않았습니다» 가 떠요</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>고장이 아닙니다. 본사가 정산·매출 › 🏢 AI 사용료에서 «자동 청구 켜기»를 하기 전(테스트 기간)에 나오는 안내입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>대리점이 이미 결제한 학생을 빼 달래요</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>대리점 화면에서는 뺄 수 없습니다. 환불은 본사가 처리합니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
